--- a/ticvai/repos/ticvai-docs/handoff/TICVAI_Schema_Merge_Tasks.xlsx
+++ b/ticvai/repos/ticvai-docs/handoff/TICVAI_Schema_Merge_Tasks.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$1:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$1:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Our actions'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tasks'!$A$1:$F$224</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Open'!$A$1:$F$1</definedName>
@@ -901,7 +901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="I2" s="18" t="inlineStr">
         <is>
-          <t>catalogue.rental_rate puts rental pricing inside the hottest table set in the system - the flash-sale argument that gave F&amp;B and Retail their own price tables. Their layout also splits rental across CatalogueService and VenueOpsService. But we hold agreement_rules and agreement_signature and NO agreement: the signature signs a version string, and rental.participant has no booking reference at all.</t>
+          <t>catalogue.rental_rate puts rental pricing inside the hottest table set in the system - catalogue.product alone is read by twelve contracts across 40 operations. Their layout also splits rental across CatalogueService and VenueOpsService. But we hold agreement_rules and agreement_signature and NO agreement: the signature signs a version string, and rental.participant has no booking reference at all.</t>
         </is>
       </c>
     </row>
@@ -1435,8 +1435,180 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Currency on nine accepted tables</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Seven genuinely differ, two are copies</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>tie</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>tie</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>ADR-0018 resolves currency from the region and does not store it, so a generated schema putting a currency column on anything holding money is supplying the conventional thing and missing the specific one. Seven of the nine are exempt for a real reason; two are copies of a fact that cannot differ and are marked not-persisted. It amended ADR-0018: a venue may set its own currency and it freezes at the first trade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>The F&amp;B and Retail catalogue</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>COLLAPSE into catalogue.* - keep six columns</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>theirs</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>We took their ten product/category/variant/price/price_list tables on a DB-strain argument and then measured it: catalogue.product has 40 operations across twelve contracts and all ten of the new tables have zero. No retail operation reads catalogue.product at all. A split that relieves contention needs the READS moved, not the tables added - we paid the whole maintenance cost and got none of the isolation. Three to one on the rubric, and the one criterion the split wins is unexercised; x-ticvai-read-routing: analytical already exists for real contention. Six of their columns stay, including product.categoryId - catalogue.product_category had two operations since 20 August and nothing could be filed under it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>The tier table decision 8 promised</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>marketing.programme_tier - and keep the cache</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>theirs</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>theirs</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>Decision 8 said retire loyalty_tier and add a real tier table; the retire happened and the add did not, so loyalty_position carried tierCode and tierName as denormalised strings and pointsToNextTier was computed from a threshold that lived nowhere. The name was the part that needed deciding: marketing.loyalty_tier is spent - schema-history declares it renamed to points_earning_rule - and marketing.tier would repeat the subscription.plan collision. The answer is BOTH the table and the cache: maintainability and readability want the table, optimised access and cross-cell want the strings, because reading a definition to render a badge would be a cross-cell call to print a word.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Inspection answers</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>maintenance.inspection_item</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>theirs</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>theirs</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>SubmitInspectionRequest.responses[] has always taken a key, a value, a pass flag, a note and attachments, tagged 'none - request only', and the only persistence ever claimed was maintenance.inspection_response, which does not exist. The template held the questions, the inspection held failedItemCount, and which check failed was accepted over the wire and dropped - on a record that takes an asset out of service. Items go on InspectionResult, the detail response, not on Inspection, the list row, and the counts stay because listInspections returns it in a list.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
+  <autoFilter ref="A1:I16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ticvai/repos/ticvai-docs/handoff/TICVAI_Schema_Merge_Tasks.xlsx
+++ b/ticvai/repos/ticvai-docs/handoff/TICVAI_Schema_Merge_Tasks.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>payroll — a scope question, not a schema one</t>
+          <t>nothing is outstanding; payroll closed on their own sources (see Decision 6)</t>
         </is>
       </c>
     </row>
